--- a/Excel/LegacySetConfig.xlsx
+++ b/Excel/LegacySetConfig.xlsx
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Role</t>
+  </si>
+  <si>
     <t>StartLevel</t>
   </si>
   <si>
@@ -47,9 +50,6 @@
     <t>AtrVueList</t>
   </si>
   <si>
-    <t>AtrRiseList</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -65,22 +65,22 @@
     <t>传世圣战</t>
   </si>
   <si>
-    <t>1001,1004,2001,2004,94</t>
-  </si>
-  <si>
-    <t>5000,2,1,1,1</t>
+    <t>1004,2004,27,94</t>
+  </si>
+  <si>
+    <t>10,2,1,1</t>
   </si>
   <si>
     <t>传世法神</t>
   </si>
   <si>
-    <t>1001,1005,2001,2005,94</t>
+    <t>1005,2005,27,94</t>
   </si>
   <si>
     <t>传世天尊</t>
   </si>
   <si>
-    <t>1001,1006,2001,2006,94</t>
+    <t>1006,2006,27,94</t>
   </si>
 </sst>
 </file>
@@ -1046,12 +1046,11 @@
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.3333333333333" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.4166666666667" style="2" customWidth="1"/>
+    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6666666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17" style="2" customWidth="1"/>
     <col min="10" max="16365" width="9" style="2"/>
     <col min="16366" max="16384" width="9" style="1"/>
   </cols>
@@ -1059,14 +1058,12 @@
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
@@ -1133,10 +1130,10 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>10</v>
@@ -1149,20 +1146,20 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>13</v>
@@ -1172,20 +1169,20 @@
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>13</v>
@@ -1195,117 +1192,118 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>10</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="D9" s="4"/>
       <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="D10" s="4"/>
       <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="D11" s="4"/>
       <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="D12" s="4"/>
       <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="D13" s="4"/>
       <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="D15" s="4"/>
       <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D17" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D18" s="4"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D19" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D20" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D21" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D22" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1"/>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D24" s="4"/>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D25" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D26" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D27" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D28" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D29" s="4"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D30" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="4:5">
-      <c r="D31" s="4"/>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="5:6">
       <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1"/>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:6 16366:16382">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7 16366:16382">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
       <c r="XEL33" s="1"/>
       <c r="XEM33" s="1"/>
       <c r="XEN33" s="1"/>
@@ -1324,11 +1322,12 @@
       <c r="XFA33" s="1"/>
       <c r="XFB33" s="1"/>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:6 16366:16382">
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7 16366:16382">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
       <c r="XEL34" s="1"/>
       <c r="XEM34" s="1"/>
       <c r="XEN34" s="1"/>
@@ -1347,11 +1346,12 @@
       <c r="XFA34" s="1"/>
       <c r="XFB34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:6 16366:16382">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:7 16366:16382">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
       <c r="XEL35" s="1"/>
       <c r="XEM35" s="1"/>
       <c r="XEN35" s="1"/>
@@ -1372,7 +1372,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 F3:I3 C4 D4 E4 F4 G4 H4 I4 C5 D5 E5 F5:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/LegacySetConfig.xlsx
+++ b/Excel/LegacySetConfig.xlsx
@@ -68,7 +68,7 @@
     <t>1004,2004,27,94</t>
   </si>
   <si>
-    <t>10,2,1,1</t>
+    <t>5,1,1,1</t>
   </si>
   <si>
     <t>传世法神</t>
